--- a/data/nzd0041/nzd0041.xlsx
+++ b/data/nzd0041/nzd0041.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K496"/>
+  <dimension ref="A1:K500"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19788,6 +19788,162 @@
         <v>381.46</v>
       </c>
       <c r="K496" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-25 22:10:44+00:00</t>
+        </is>
+      </c>
+      <c r="B497" t="n">
+        <v>382.14</v>
+      </c>
+      <c r="C497" t="n">
+        <v>370.01</v>
+      </c>
+      <c r="D497" t="n">
+        <v>364.88</v>
+      </c>
+      <c r="E497" t="n">
+        <v>367.97</v>
+      </c>
+      <c r="F497" t="n">
+        <v>371.36</v>
+      </c>
+      <c r="G497" t="n">
+        <v>378.04</v>
+      </c>
+      <c r="H497" t="n">
+        <v>377.49</v>
+      </c>
+      <c r="I497" t="n">
+        <v>375.65</v>
+      </c>
+      <c r="J497" t="n">
+        <v>381.46</v>
+      </c>
+      <c r="K497" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-10 22:17:07+00:00</t>
+        </is>
+      </c>
+      <c r="B498" t="n">
+        <v>385.46</v>
+      </c>
+      <c r="C498" t="n">
+        <v>369.61</v>
+      </c>
+      <c r="D498" t="n">
+        <v>365.11</v>
+      </c>
+      <c r="E498" t="n">
+        <v>367.85</v>
+      </c>
+      <c r="F498" t="n">
+        <v>371.38</v>
+      </c>
+      <c r="G498" t="n">
+        <v>377.87</v>
+      </c>
+      <c r="H498" t="n">
+        <v>377.31</v>
+      </c>
+      <c r="I498" t="n">
+        <v>375.65</v>
+      </c>
+      <c r="J498" t="n">
+        <v>381.4</v>
+      </c>
+      <c r="K498" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:10:49+00:00</t>
+        </is>
+      </c>
+      <c r="B499" t="n">
+        <v>387.11</v>
+      </c>
+      <c r="C499" t="n">
+        <v>369.88</v>
+      </c>
+      <c r="D499" t="n">
+        <v>365.53</v>
+      </c>
+      <c r="E499" t="n">
+        <v>368.32</v>
+      </c>
+      <c r="F499" t="n">
+        <v>371.67</v>
+      </c>
+      <c r="G499" t="n">
+        <v>378.04</v>
+      </c>
+      <c r="H499" t="n">
+        <v>377.82</v>
+      </c>
+      <c r="I499" t="n">
+        <v>376.11</v>
+      </c>
+      <c r="J499" t="n">
+        <v>381.54</v>
+      </c>
+      <c r="K499" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-26 22:17:20+00:00</t>
+        </is>
+      </c>
+      <c r="B500" t="n">
+        <v>387.31</v>
+      </c>
+      <c r="C500" t="n">
+        <v>369.86</v>
+      </c>
+      <c r="D500" t="n">
+        <v>365.64</v>
+      </c>
+      <c r="E500" t="n">
+        <v>369.2</v>
+      </c>
+      <c r="F500" t="n">
+        <v>372.46</v>
+      </c>
+      <c r="G500" t="n">
+        <v>378.67</v>
+      </c>
+      <c r="H500" t="n">
+        <v>378.84</v>
+      </c>
+      <c r="I500" t="n">
+        <v>376.55</v>
+      </c>
+      <c r="J500" t="n">
+        <v>382.23</v>
+      </c>
+      <c r="K500" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -19804,7 +19960,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B591"/>
+  <dimension ref="A1:B595"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25717,6 +25873,46 @@
       </c>
       <c r="B591" t="n">
         <v>0.89</v>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" t="inlineStr">
+        <is>
+          <t>2026-06-25 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B592" t="n">
+        <v>-0.72</v>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" t="inlineStr">
+        <is>
+          <t>2026-07-10 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B593" t="n">
+        <v>-0.92</v>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B594" t="n">
+        <v>-0.9</v>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" t="inlineStr">
+        <is>
+          <t>2026-07-26 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B595" t="n">
+        <v>-0.5600000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -25885,28 +26081,28 @@
         <v>0.0346</v>
       </c>
       <c r="I2" t="n">
-        <v>0.478480911177651</v>
+        <v>0.4730979582036364</v>
       </c>
       <c r="J2" t="n">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="K2" t="n">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1551961693815299</v>
+        <v>0.1541029219038474</v>
       </c>
       <c r="M2" t="n">
-        <v>6.83145820638271</v>
+        <v>6.802437146779893</v>
       </c>
       <c r="N2" t="n">
-        <v>78.31866139473274</v>
+        <v>77.83788074956126</v>
       </c>
       <c r="O2" t="n">
-        <v>8.849783126988635</v>
+        <v>8.822577897052611</v>
       </c>
       <c r="P2" t="n">
-        <v>376.4356990028047</v>
+        <v>376.4896869256891</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -25963,28 +26159,28 @@
         <v>0.1183</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2333518552838036</v>
+        <v>0.2264035300060099</v>
       </c>
       <c r="J3" t="n">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="K3" t="n">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2227996122004603</v>
+        <v>0.2125746832708816</v>
       </c>
       <c r="M3" t="n">
-        <v>2.70766108785667</v>
+        <v>2.722598504397093</v>
       </c>
       <c r="N3" t="n">
-        <v>11.93719368805734</v>
+        <v>12.0294681106063</v>
       </c>
       <c r="O3" t="n">
-        <v>3.455024412078349</v>
+        <v>3.468352362521188</v>
       </c>
       <c r="P3" t="n">
-        <v>368.4611456968228</v>
+        <v>368.5308853601672</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -26041,28 +26237,28 @@
         <v>0.109</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2296608343254532</v>
+        <v>0.2260086166056778</v>
       </c>
       <c r="J4" t="n">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="K4" t="n">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1762743430269212</v>
+        <v>0.173485754791091</v>
       </c>
       <c r="M4" t="n">
-        <v>3.056511313589172</v>
+        <v>3.052473286260746</v>
       </c>
       <c r="N4" t="n">
-        <v>15.4891830185921</v>
+        <v>15.41766913400723</v>
       </c>
       <c r="O4" t="n">
-        <v>3.93562993923363</v>
+        <v>3.926533984827742</v>
       </c>
       <c r="P4" t="n">
-        <v>361.6894198458444</v>
+        <v>361.7260704538762</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -26119,28 +26315,28 @@
         <v>0.1474</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2665099020001257</v>
+        <v>0.2641734829103255</v>
       </c>
       <c r="J5" t="n">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="K5" t="n">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2564175939971574</v>
+        <v>0.2557927396887586</v>
       </c>
       <c r="M5" t="n">
-        <v>2.831094358519489</v>
+        <v>2.820993521786366</v>
       </c>
       <c r="N5" t="n">
-        <v>12.94401864914501</v>
+        <v>12.86371286148097</v>
       </c>
       <c r="O5" t="n">
-        <v>3.597779683241458</v>
+        <v>3.586601854329662</v>
       </c>
       <c r="P5" t="n">
-        <v>362.817157822125</v>
+        <v>362.8405985439455</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -26197,28 +26393,28 @@
         <v>0.1387</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2258989766372944</v>
+        <v>0.2219739030933904</v>
       </c>
       <c r="J6" t="n">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="K6" t="n">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1491986354405659</v>
+        <v>0.1463916266648447</v>
       </c>
       <c r="M6" t="n">
-        <v>3.271621616090395</v>
+        <v>3.265263155047196</v>
       </c>
       <c r="N6" t="n">
-        <v>18.28744360832039</v>
+        <v>18.20239235045894</v>
       </c>
       <c r="O6" t="n">
-        <v>4.276382069965264</v>
+        <v>4.266426180125344</v>
       </c>
       <c r="P6" t="n">
-        <v>368.4083263599169</v>
+        <v>368.4477129556275</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -26275,28 +26471,28 @@
         <v>0.1225</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1711869277505046</v>
+        <v>0.1671316940545853</v>
       </c>
       <c r="J7" t="n">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="K7" t="n">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="L7" t="n">
-        <v>0.09726876830549391</v>
+        <v>0.09418707861958375</v>
       </c>
       <c r="M7" t="n">
-        <v>3.01013653614933</v>
+        <v>3.008872996482051</v>
       </c>
       <c r="N7" t="n">
-        <v>17.09178390814932</v>
+        <v>17.01950871316845</v>
       </c>
       <c r="O7" t="n">
-        <v>4.134221076351545</v>
+        <v>4.125470726252757</v>
       </c>
       <c r="P7" t="n">
-        <v>376.4113025604857</v>
+        <v>376.4519991018229</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -26353,28 +26549,28 @@
         <v>0.1273</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1520321390328856</v>
+        <v>0.1449080950104597</v>
       </c>
       <c r="J8" t="n">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="K8" t="n">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="L8" t="n">
-        <v>0.05527946227937519</v>
+        <v>0.05086300068509331</v>
       </c>
       <c r="M8" t="n">
-        <v>3.948511354321732</v>
+        <v>3.956901949604605</v>
       </c>
       <c r="N8" t="n">
-        <v>24.82398527839165</v>
+        <v>24.82529534411647</v>
       </c>
       <c r="O8" t="n">
-        <v>4.982367437111765</v>
+        <v>4.98249890558106</v>
       </c>
       <c r="P8" t="n">
-        <v>378.8009467598054</v>
+        <v>378.8724386148899</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -26431,28 +26627,28 @@
         <v>0.0502</v>
       </c>
       <c r="I9" t="n">
-        <v>0.04634292573554102</v>
+        <v>0.03970503855929258</v>
       </c>
       <c r="J9" t="n">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="K9" t="n">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="L9" t="n">
-        <v>0.006844543789681024</v>
+        <v>0.005070134650661084</v>
       </c>
       <c r="M9" t="n">
-        <v>3.507162991758038</v>
+        <v>3.515230874804041</v>
       </c>
       <c r="N9" t="n">
-        <v>19.58397154699123</v>
+        <v>19.59956455134099</v>
       </c>
       <c r="O9" t="n">
-        <v>4.425378124747221</v>
+        <v>4.427139545049489</v>
       </c>
       <c r="P9" t="n">
-        <v>379.4238434291582</v>
+        <v>379.4904592074143</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -26509,28 +26705,28 @@
         <v>0.0552</v>
       </c>
       <c r="I10" t="n">
-        <v>0.06844447937711504</v>
+        <v>0.06193509417125297</v>
       </c>
       <c r="J10" t="n">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="K10" t="n">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="L10" t="n">
-        <v>0.02212580007450282</v>
+        <v>0.01825102290642466</v>
       </c>
       <c r="M10" t="n">
-        <v>2.949964711373867</v>
+        <v>2.963538700702167</v>
       </c>
       <c r="N10" t="n">
-        <v>13.01133920744488</v>
+        <v>13.07281321468812</v>
       </c>
       <c r="O10" t="n">
-        <v>3.607123397867736</v>
+        <v>3.615634552148229</v>
       </c>
       <c r="P10" t="n">
-        <v>384.406990843766</v>
+        <v>384.4723179178142</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -26568,7 +26764,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K496"/>
+  <dimension ref="A1:K500"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -54843,6 +55039,234 @@
         </is>
       </c>
     </row>
+    <row r="497">
+      <c r="A497" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-25 22:10:44+00:00</t>
+        </is>
+      </c>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>-34.98901023434432,173.47987950703506</t>
+        </is>
+      </c>
+      <c r="C497" t="inlineStr">
+        <is>
+          <t>-34.98952681573046,173.48049211177397</t>
+        </is>
+      </c>
+      <c r="D497" t="inlineStr">
+        <is>
+          <t>-34.98967107855008,173.48134912171392</t>
+        </is>
+      </c>
+      <c r="E497" t="inlineStr">
+        <is>
+          <t>-34.989800114488766,173.48223556942105</t>
+        </is>
+      </c>
+      <c r="F497" t="inlineStr">
+        <is>
+          <t>-34.99002519826078,173.48309177365354</t>
+        </is>
+      </c>
+      <c r="G497" t="inlineStr">
+        <is>
+          <t>-34.99016804728391,173.48395914400297</t>
+        </is>
+      </c>
+      <c r="H497" t="inlineStr">
+        <is>
+          <t>-34.99026594661351,173.4848238197652</t>
+        </is>
+      </c>
+      <c r="I497" t="inlineStr">
+        <is>
+          <t>-34.99027209560058,173.485718905153</t>
+        </is>
+      </c>
+      <c r="J497" t="inlineStr">
+        <is>
+          <t>-34.99030495461206,173.48661733535502</t>
+        </is>
+      </c>
+      <c r="K497" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-10 22:17:07+00:00</t>
+        </is>
+      </c>
+      <c r="B498" t="inlineStr">
+        <is>
+          <t>-34.98898629166075,173.47990134486753</t>
+        </is>
+      </c>
+      <c r="C498" t="inlineStr">
+        <is>
+          <t>-34.989530151059526,173.48049044334087</t>
+        </is>
+      </c>
+      <c r="D498" t="inlineStr">
+        <is>
+          <t>-34.98966903608419,173.4813495592718</t>
+        </is>
+      </c>
+      <c r="E498" t="inlineStr">
+        <is>
+          <t>-34.98980115439715,173.48223520597077</t>
+        </is>
+      </c>
+      <c r="F498" t="inlineStr">
+        <is>
+          <t>-34.99002502673384,173.4830918413392</t>
+        </is>
+      </c>
+      <c r="G498" t="inlineStr">
+        <is>
+          <t>-34.990169548716786,173.48395876834087</t>
+        </is>
+      </c>
+      <c r="H498" t="inlineStr">
+        <is>
+          <t>-34.99026756725863,173.48482371126713</t>
+        </is>
+      </c>
+      <c r="I498" t="inlineStr">
+        <is>
+          <t>-34.99027209560058,173.485718905153</t>
+        </is>
+      </c>
+      <c r="J498" t="inlineStr">
+        <is>
+          <t>-34.99030549218307,173.48661726108836</t>
+        </is>
+      </c>
+      <c r="K498" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:10:49+00:00</t>
+        </is>
+      </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>-34.98897439243402,173.47991219800244</t>
+        </is>
+      </c>
+      <c r="C499" t="inlineStr">
+        <is>
+          <t>-34.9895278997124,173.48049156953323</t>
+        </is>
+      </c>
+      <c r="D499" t="inlineStr">
+        <is>
+          <t>-34.989665306363854,173.48135035829046</t>
+        </is>
+      </c>
+      <c r="E499" t="inlineStr">
+        <is>
+          <t>-34.9897970814226,173.4822366294843</t>
+        </is>
+      </c>
+      <c r="F499" t="inlineStr">
+        <is>
+          <t>-34.99002253959313,173.4830928227806</t>
+        </is>
+      </c>
+      <c r="G499" t="inlineStr">
+        <is>
+          <t>-34.99016804728391,173.48395914400297</t>
+        </is>
+      </c>
+      <c r="H499" t="inlineStr">
+        <is>
+          <t>-34.990262975430795,173.48482401867835</t>
+        </is>
+      </c>
+      <c r="I499" t="inlineStr">
+        <is>
+          <t>-34.99026795237659,173.48571914516216</t>
+        </is>
+      </c>
+      <c r="J499" t="inlineStr">
+        <is>
+          <t>-34.99030423785069,173.48661743437722</t>
+        </is>
+      </c>
+      <c r="K499" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-26 22:17:20+00:00</t>
+        </is>
+      </c>
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>-34.988972950103445,173.47991351353375</t>
+        </is>
+      </c>
+      <c r="C500" t="inlineStr">
+        <is>
+          <t>-34.989528066478854,173.48049148611156</t>
+        </is>
+      </c>
+      <c r="D500" t="inlineStr">
+        <is>
+          <t>-34.98966432953233,173.48135056755726</t>
+        </is>
+      </c>
+      <c r="E500" t="inlineStr">
+        <is>
+          <t>-34.98978945542764,173.48223929478584</t>
+        </is>
+      </c>
+      <c r="F500" t="inlineStr">
+        <is>
+          <t>-34.99001576427879,173.48309549636215</t>
+        </is>
+      </c>
+      <c r="G500" t="inlineStr">
+        <is>
+          <t>-34.99016248315031,173.4839605361625</t>
+        </is>
+      </c>
+      <c r="H500" t="inlineStr">
+        <is>
+          <t>-34.990253791775125,173.48482463350072</t>
+        </is>
+      </c>
+      <c r="I500" t="inlineStr">
+        <is>
+          <t>-34.99026398929278,173.4857193747361</t>
+        </is>
+      </c>
+      <c r="J500" t="inlineStr">
+        <is>
+          <t>-34.990298055784024,173.48661828844362</t>
+        </is>
+      </c>
+      <c r="K500" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0041/nzd0041.xlsx
+++ b/data/nzd0041/nzd0041.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K500"/>
+  <dimension ref="A1:K504"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19944,6 +19944,162 @@
         <v>382.23</v>
       </c>
       <c r="K500" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:11:00+00:00</t>
+        </is>
+      </c>
+      <c r="B501" t="n">
+        <v>386</v>
+      </c>
+      <c r="C501" t="n">
+        <v>370.37</v>
+      </c>
+      <c r="D501" t="n">
+        <v>366.29</v>
+      </c>
+      <c r="E501" t="n">
+        <v>369.5</v>
+      </c>
+      <c r="F501" t="n">
+        <v>372.77</v>
+      </c>
+      <c r="G501" t="n">
+        <v>379.07</v>
+      </c>
+      <c r="H501" t="n">
+        <v>379.51</v>
+      </c>
+      <c r="I501" t="n">
+        <v>376.81</v>
+      </c>
+      <c r="J501" t="n">
+        <v>382.74</v>
+      </c>
+      <c r="K501" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B502" t="n">
+        <v>385.84</v>
+      </c>
+      <c r="C502" t="n">
+        <v>370.96</v>
+      </c>
+      <c r="D502" t="n">
+        <v>366.67</v>
+      </c>
+      <c r="E502" t="n">
+        <v>369.89</v>
+      </c>
+      <c r="F502" t="n">
+        <v>372.95</v>
+      </c>
+      <c r="G502" t="n">
+        <v>379.74</v>
+      </c>
+      <c r="H502" t="n">
+        <v>379.57</v>
+      </c>
+      <c r="I502" t="n">
+        <v>376.69</v>
+      </c>
+      <c r="J502" t="n">
+        <v>383.13</v>
+      </c>
+      <c r="K502" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:17:20+00:00</t>
+        </is>
+      </c>
+      <c r="B503" t="n">
+        <v>386.43</v>
+      </c>
+      <c r="C503" t="n">
+        <v>371.24</v>
+      </c>
+      <c r="D503" t="n">
+        <v>366.87</v>
+      </c>
+      <c r="E503" t="n">
+        <v>369.96</v>
+      </c>
+      <c r="F503" t="n">
+        <v>373.39</v>
+      </c>
+      <c r="G503" t="n">
+        <v>379.64</v>
+      </c>
+      <c r="H503" t="n">
+        <v>379.68</v>
+      </c>
+      <c r="I503" t="n">
+        <v>375.92</v>
+      </c>
+      <c r="J503" t="n">
+        <v>383.2</v>
+      </c>
+      <c r="K503" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B504" t="n">
+        <v>388.71</v>
+      </c>
+      <c r="C504" t="n">
+        <v>371.6</v>
+      </c>
+      <c r="D504" t="n">
+        <v>366.92</v>
+      </c>
+      <c r="E504" t="n">
+        <v>370.07</v>
+      </c>
+      <c r="F504" t="n">
+        <v>373.57</v>
+      </c>
+      <c r="G504" t="n">
+        <v>379.93</v>
+      </c>
+      <c r="H504" t="n">
+        <v>380</v>
+      </c>
+      <c r="I504" t="n">
+        <v>375.27</v>
+      </c>
+      <c r="J504" t="n">
+        <v>383.53</v>
+      </c>
+      <c r="K504" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -19960,7 +20116,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B595"/>
+  <dimension ref="A1:B599"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25913,6 +26069,46 @@
       </c>
       <c r="B595" t="n">
         <v>-0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B596" t="n">
+        <v>-0.32</v>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B597" t="n">
+        <v>0.38</v>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B598" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B599" t="n">
+        <v>-0.28</v>
       </c>
     </row>
   </sheetData>
@@ -26081,28 +26277,28 @@
         <v>0.0346</v>
       </c>
       <c r="I2" t="n">
-        <v>0.4730979582036364</v>
+        <v>0.4696008911871153</v>
       </c>
       <c r="J2" t="n">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="K2" t="n">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1541029219038474</v>
+        <v>0.1541383500765783</v>
       </c>
       <c r="M2" t="n">
-        <v>6.802437146779893</v>
+        <v>6.765056898026379</v>
       </c>
       <c r="N2" t="n">
-        <v>77.83788074956126</v>
+        <v>77.27821729410158</v>
       </c>
       <c r="O2" t="n">
-        <v>8.822577897052611</v>
+        <v>8.790802994840778</v>
       </c>
       <c r="P2" t="n">
-        <v>376.4896869256891</v>
+        <v>376.5249153701747</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -26159,28 +26355,28 @@
         <v>0.1183</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2264035300060099</v>
+        <v>0.2213886784261192</v>
       </c>
       <c r="J3" t="n">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="K3" t="n">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2125746832708816</v>
+        <v>0.2063769390164238</v>
       </c>
       <c r="M3" t="n">
-        <v>2.722598504397093</v>
+        <v>2.727089967016958</v>
       </c>
       <c r="N3" t="n">
-        <v>12.0294681106063</v>
+        <v>12.03578908750893</v>
       </c>
       <c r="O3" t="n">
-        <v>3.468352362521188</v>
+        <v>3.469263479113244</v>
       </c>
       <c r="P3" t="n">
-        <v>368.5308853601672</v>
+        <v>368.5814176566594</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -26237,28 +26433,28 @@
         <v>0.109</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2260086166056778</v>
+        <v>0.2244240767381766</v>
       </c>
       <c r="J4" t="n">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="K4" t="n">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="L4" t="n">
-        <v>0.173485754791091</v>
+        <v>0.1736464590943612</v>
       </c>
       <c r="M4" t="n">
-        <v>3.052473286260746</v>
+        <v>3.03708498262515</v>
       </c>
       <c r="N4" t="n">
-        <v>15.41766913400723</v>
+        <v>15.30556957150212</v>
       </c>
       <c r="O4" t="n">
-        <v>3.926533984827742</v>
+        <v>3.912233322732952</v>
       </c>
       <c r="P4" t="n">
-        <v>361.7260704538762</v>
+        <v>361.7420351032639</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -26315,28 +26511,28 @@
         <v>0.1474</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2641734829103255</v>
+        <v>0.2640137359286214</v>
       </c>
       <c r="J5" t="n">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="K5" t="n">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2557927396887586</v>
+        <v>0.2585882306032119</v>
       </c>
       <c r="M5" t="n">
-        <v>2.820993521786366</v>
+        <v>2.799811550069844</v>
       </c>
       <c r="N5" t="n">
-        <v>12.86371286148097</v>
+        <v>12.76187267869242</v>
       </c>
       <c r="O5" t="n">
-        <v>3.586601854329662</v>
+        <v>3.572376334975421</v>
       </c>
       <c r="P5" t="n">
-        <v>362.8405985439455</v>
+        <v>362.8422047846189</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -26393,28 +26589,28 @@
         <v>0.1387</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2219739030933904</v>
+        <v>0.2202077484157706</v>
       </c>
       <c r="J6" t="n">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="K6" t="n">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1463916266648447</v>
+        <v>0.1462876974657641</v>
       </c>
       <c r="M6" t="n">
-        <v>3.265263155047196</v>
+        <v>3.248186495703993</v>
       </c>
       <c r="N6" t="n">
-        <v>18.20239235045894</v>
+        <v>18.07089111934838</v>
       </c>
       <c r="O6" t="n">
-        <v>4.266426180125344</v>
+        <v>4.250987075885833</v>
       </c>
       <c r="P6" t="n">
-        <v>368.4477129556275</v>
+        <v>368.4655064743528</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -26471,28 +26667,28 @@
         <v>0.1225</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1671316940545853</v>
+        <v>0.1652264618302527</v>
       </c>
       <c r="J7" t="n">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="K7" t="n">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="L7" t="n">
-        <v>0.09418707861958375</v>
+        <v>0.0935103617979588</v>
       </c>
       <c r="M7" t="n">
-        <v>3.008872996482051</v>
+        <v>2.995565622015149</v>
       </c>
       <c r="N7" t="n">
-        <v>17.01950871316845</v>
+        <v>16.89946490565958</v>
       </c>
       <c r="O7" t="n">
-        <v>4.125470726252757</v>
+        <v>4.110895876285312</v>
       </c>
       <c r="P7" t="n">
-        <v>376.4519991018229</v>
+        <v>376.4711954738768</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -26549,28 +26745,28 @@
         <v>0.1273</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1449080950104597</v>
+        <v>0.1405937626141022</v>
       </c>
       <c r="J8" t="n">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="K8" t="n">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="L8" t="n">
-        <v>0.05086300068509331</v>
+        <v>0.0486138314204756</v>
       </c>
       <c r="M8" t="n">
-        <v>3.956901949604605</v>
+        <v>3.950059521285552</v>
       </c>
       <c r="N8" t="n">
-        <v>24.82529534411647</v>
+        <v>24.7024330599458</v>
       </c>
       <c r="O8" t="n">
-        <v>4.98249890558106</v>
+        <v>4.970154228989861</v>
       </c>
       <c r="P8" t="n">
-        <v>378.8724386148899</v>
+        <v>378.9159162801054</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -26627,28 +26823,28 @@
         <v>0.0502</v>
       </c>
       <c r="I9" t="n">
-        <v>0.03970503855929258</v>
+        <v>0.03357983206443488</v>
       </c>
       <c r="J9" t="n">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="K9" t="n">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="L9" t="n">
-        <v>0.005070134650661084</v>
+        <v>0.003660991251656087</v>
       </c>
       <c r="M9" t="n">
-        <v>3.515230874804041</v>
+        <v>3.521408278222524</v>
       </c>
       <c r="N9" t="n">
-        <v>19.59956455134099</v>
+        <v>19.59639223901209</v>
       </c>
       <c r="O9" t="n">
-        <v>4.427139545049489</v>
+        <v>4.426781250413453</v>
       </c>
       <c r="P9" t="n">
-        <v>379.4904592074143</v>
+        <v>379.5522015126968</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -26705,28 +26901,28 @@
         <v>0.0552</v>
       </c>
       <c r="I10" t="n">
-        <v>0.06193509417125297</v>
+        <v>0.05776105812605289</v>
       </c>
       <c r="J10" t="n">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="K10" t="n">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="L10" t="n">
-        <v>0.01825102290642466</v>
+        <v>0.01607672759311729</v>
       </c>
       <c r="M10" t="n">
-        <v>2.963538700702167</v>
+        <v>2.963690112506149</v>
       </c>
       <c r="N10" t="n">
-        <v>13.07281321468812</v>
+        <v>13.0390064947457</v>
       </c>
       <c r="O10" t="n">
-        <v>3.615634552148229</v>
+        <v>3.610956451516094</v>
       </c>
       <c r="P10" t="n">
-        <v>384.4723179178142</v>
+        <v>384.5143797916364</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -26764,7 +26960,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K500"/>
+  <dimension ref="A1:K504"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55267,6 +55463,234 @@
         </is>
       </c>
     </row>
+    <row r="501">
+      <c r="A501" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:11:00+00:00</t>
+        </is>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>-34.98898239736847,173.47990489680294</t>
+        </is>
+      </c>
+      <c r="C501" t="inlineStr">
+        <is>
+          <t>-34.98952381393429,173.48049361336362</t>
+        </is>
+      </c>
+      <c r="D501" t="inlineStr">
+        <is>
+          <t>-34.98965855734608,173.48135180413357</t>
+        </is>
+      </c>
+      <c r="E501" t="inlineStr">
+        <is>
+          <t>-34.98978685565663,173.48224020341127</t>
+        </is>
+      </c>
+      <c r="F501" t="inlineStr">
+        <is>
+          <t>-34.9900131056111,173.48309654548896</t>
+        </is>
+      </c>
+      <c r="G501" t="inlineStr">
+        <is>
+          <t>-34.99015895036706,173.48396142007323</t>
+        </is>
+      </c>
+      <c r="H501" t="inlineStr">
+        <is>
+          <t>-34.99024775937385,173.48482503735457</t>
+        </is>
+      </c>
+      <c r="I501" t="inlineStr">
+        <is>
+          <t>-34.99026164747053,173.4857195103934</t>
+        </is>
+      </c>
+      <c r="J501" t="inlineStr">
+        <is>
+          <t>-34.9902934864304,173.48661891971003</t>
+        </is>
+      </c>
+      <c r="K501" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>-34.988983551232856,173.47990384437767</t>
+        </is>
+      </c>
+      <c r="C502" t="inlineStr">
+        <is>
+          <t>-34.989518894323844,173.480496074302</t>
+        </is>
+      </c>
+      <c r="D502" t="inlineStr">
+        <is>
+          <t>-34.98965518283718,173.48135252705507</t>
+        </is>
+      </c>
+      <c r="E502" t="inlineStr">
+        <is>
+          <t>-34.98978347595428,173.48224138462422</t>
+        </is>
+      </c>
+      <c r="F502" t="inlineStr">
+        <is>
+          <t>-34.99001156186857,173.48309715465933</t>
+        </is>
+      </c>
+      <c r="G502" t="inlineStr">
+        <is>
+          <t>-34.99015303295512,173.48396290062348</t>
+        </is>
+      </c>
+      <c r="H502" t="inlineStr">
+        <is>
+          <t>-34.99024721915881,173.48482507352057</t>
+        </is>
+      </c>
+      <c r="I502" t="inlineStr">
+        <is>
+          <t>-34.99026272831157,173.48571944778237</t>
+        </is>
+      </c>
+      <c r="J502" t="inlineStr">
+        <is>
+          <t>-34.990289992218806,173.48661940244313</t>
+        </is>
+      </c>
+      <c r="K502" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:17:20+00:00</t>
+        </is>
+      </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>-34.988979296357876,173.47990772519572</t>
+        </is>
+      </c>
+      <c r="C503" t="inlineStr">
+        <is>
+          <t>-34.989516559593454,173.48049724220488</t>
+        </is>
+      </c>
+      <c r="D503" t="inlineStr">
+        <is>
+          <t>-34.98965340677988,173.48135290754004</t>
+        </is>
+      </c>
+      <c r="E503" t="inlineStr">
+        <is>
+          <t>-34.989782869341035,173.48224159663678</t>
+        </is>
+      </c>
+      <c r="F503" t="inlineStr">
+        <is>
+          <t>-34.99000778827571,173.48309864374238</t>
+        </is>
+      </c>
+      <c r="G503" t="inlineStr">
+        <is>
+          <t>-34.99015391615092,173.48396267964586</t>
+        </is>
+      </c>
+      <c r="H503" t="inlineStr">
+        <is>
+          <t>-34.990246228764576,173.48482513982495</t>
+        </is>
+      </c>
+      <c r="I503" t="inlineStr">
+        <is>
+          <t>-34.990269663708226,173.48571904602792</t>
+        </is>
+      </c>
+      <c r="J503" t="inlineStr">
+        <is>
+          <t>-34.990289365052625,173.48661948908753</t>
+        </is>
+      </c>
+      <c r="K503" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>-34.98896285378898,173.47992272225147</t>
+        </is>
+      </c>
+      <c r="C504" t="inlineStr">
+        <is>
+          <t>-34.989513557797224,173.48049874379416</t>
+        </is>
+      </c>
+      <c r="D504" t="inlineStr">
+        <is>
+          <t>-34.98965296276554,173.48135300266125</t>
+        </is>
+      </c>
+      <c r="E504" t="inlineStr">
+        <is>
+          <t>-34.98978191609165,173.4822419297994</t>
+        </is>
+      </c>
+      <c r="F504" t="inlineStr">
+        <is>
+          <t>-34.99000624453316,173.4830992529127</t>
+        </is>
+      </c>
+      <c r="G504" t="inlineStr">
+        <is>
+          <t>-34.99015135488307,173.48396332048097</t>
+        </is>
+      </c>
+      <c r="H504" t="inlineStr">
+        <is>
+          <t>-34.99024334761768,173.48482533271033</t>
+        </is>
+      </c>
+      <c r="I504" t="inlineStr">
+        <is>
+          <t>-34.99027551826385,173.48571870688454</t>
+        </is>
+      </c>
+      <c r="J504" t="inlineStr">
+        <is>
+          <t>-34.99028640841203,173.48661989755394</t>
+        </is>
+      </c>
+      <c r="K504" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0041/nzd0041.xlsx
+++ b/data/nzd0041/nzd0041.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K504"/>
+  <dimension ref="A1:K506"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20100,6 +20100,84 @@
         <v>383.53</v>
       </c>
       <c r="K504" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-05 22:11:21+00:00</t>
+        </is>
+      </c>
+      <c r="B505" t="n">
+        <v>389.9</v>
+      </c>
+      <c r="C505" t="n">
+        <v>371.74</v>
+      </c>
+      <c r="D505" t="n">
+        <v>367.16</v>
+      </c>
+      <c r="E505" t="n">
+        <v>370.44</v>
+      </c>
+      <c r="F505" t="n">
+        <v>373.26</v>
+      </c>
+      <c r="G505" t="n">
+        <v>379.86</v>
+      </c>
+      <c r="H505" t="n">
+        <v>380.28</v>
+      </c>
+      <c r="I505" t="n">
+        <v>374.78</v>
+      </c>
+      <c r="J505" t="n">
+        <v>383.56</v>
+      </c>
+      <c r="K505" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-28 22:17:40+00:00</t>
+        </is>
+      </c>
+      <c r="B506" t="n">
+        <v>391.8</v>
+      </c>
+      <c r="C506" t="n">
+        <v>372.9</v>
+      </c>
+      <c r="D506" t="n">
+        <v>368.26</v>
+      </c>
+      <c r="E506" t="n">
+        <v>371.17</v>
+      </c>
+      <c r="F506" t="n">
+        <v>374.18</v>
+      </c>
+      <c r="G506" t="n">
+        <v>380.82</v>
+      </c>
+      <c r="H506" t="n">
+        <v>380.51</v>
+      </c>
+      <c r="I506" t="n">
+        <v>374.55</v>
+      </c>
+      <c r="J506" t="n">
+        <v>383.87</v>
+      </c>
+      <c r="K506" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -20116,7 +20194,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B599"/>
+  <dimension ref="A1:B601"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26109,6 +26187,26 @@
       </c>
       <c r="B599" t="n">
         <v>-0.28</v>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" t="inlineStr">
+        <is>
+          <t>2026-09-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B600" t="n">
+        <v>-0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" t="inlineStr">
+        <is>
+          <t>2026-09-28 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B601" t="n">
+        <v>0.79</v>
       </c>
     </row>
   </sheetData>
@@ -26277,28 +26375,28 @@
         <v>0.0346</v>
       </c>
       <c r="I2" t="n">
-        <v>0.4696008911871153</v>
+        <v>0.4707193572576341</v>
       </c>
       <c r="J2" t="n">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="K2" t="n">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1541383500765783</v>
+        <v>0.1557722523709308</v>
       </c>
       <c r="M2" t="n">
-        <v>6.765056898026379</v>
+        <v>6.74557207095499</v>
       </c>
       <c r="N2" t="n">
-        <v>77.27821729410158</v>
+        <v>76.98569640874027</v>
       </c>
       <c r="O2" t="n">
-        <v>8.790802994840778</v>
+        <v>8.774149326786059</v>
       </c>
       <c r="P2" t="n">
-        <v>376.5249153701747</v>
+        <v>376.5135746444818</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -26355,28 +26453,28 @@
         <v>0.1183</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2213886784261192</v>
+        <v>0.2198189119299991</v>
       </c>
       <c r="J3" t="n">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="K3" t="n">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2063769390164238</v>
+        <v>0.2050523416803521</v>
       </c>
       <c r="M3" t="n">
-        <v>2.727089967016958</v>
+        <v>2.724420893989389</v>
       </c>
       <c r="N3" t="n">
-        <v>12.03578908750893</v>
+        <v>12.0093724195069</v>
       </c>
       <c r="O3" t="n">
-        <v>3.469263479113244</v>
+        <v>3.465454143327667</v>
       </c>
       <c r="P3" t="n">
-        <v>368.5814176566594</v>
+        <v>368.5973135311663</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -26433,28 +26531,28 @@
         <v>0.109</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2244240767381766</v>
+        <v>0.2243496362901629</v>
       </c>
       <c r="J4" t="n">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="K4" t="n">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1736464590943612</v>
+        <v>0.1746752918422091</v>
       </c>
       <c r="M4" t="n">
-        <v>3.03708498262515</v>
+        <v>3.02719502884028</v>
       </c>
       <c r="N4" t="n">
-        <v>15.30556957150212</v>
+        <v>15.24616140229221</v>
       </c>
       <c r="O4" t="n">
-        <v>3.912233322732952</v>
+        <v>3.90463332494771</v>
       </c>
       <c r="P4" t="n">
-        <v>361.7420351032639</v>
+        <v>361.7427832095049</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -26511,28 +26609,28 @@
         <v>0.1474</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2640137359286214</v>
+        <v>0.2645800631802903</v>
       </c>
       <c r="J5" t="n">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="K5" t="n">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2585882306032119</v>
+        <v>0.2608835066160848</v>
       </c>
       <c r="M5" t="n">
-        <v>2.799811550069844</v>
+        <v>2.792090863066103</v>
       </c>
       <c r="N5" t="n">
-        <v>12.76187267869242</v>
+        <v>12.71443031910007</v>
       </c>
       <c r="O5" t="n">
-        <v>3.572376334975421</v>
+        <v>3.565729984042548</v>
       </c>
       <c r="P5" t="n">
-        <v>362.8422047846189</v>
+        <v>362.8364637381652</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -26589,28 +26687,28 @@
         <v>0.1387</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2202077484157706</v>
+        <v>0.2197146362006925</v>
       </c>
       <c r="J6" t="n">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="K6" t="n">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1462876974657641</v>
+        <v>0.1466949191185454</v>
       </c>
       <c r="M6" t="n">
-        <v>3.248186495703993</v>
+        <v>3.237821406280365</v>
       </c>
       <c r="N6" t="n">
-        <v>18.07089111934838</v>
+        <v>18.00211949126451</v>
       </c>
       <c r="O6" t="n">
-        <v>4.250987075885833</v>
+        <v>4.242890464207686</v>
       </c>
       <c r="P6" t="n">
-        <v>368.4655064743528</v>
+        <v>368.4704968010977</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -26667,28 +26765,28 @@
         <v>0.1225</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1652264618302527</v>
+        <v>0.1648057115186021</v>
       </c>
       <c r="J7" t="n">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="K7" t="n">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0935103617979588</v>
+        <v>0.09373586847904081</v>
       </c>
       <c r="M7" t="n">
-        <v>2.995565622015149</v>
+        <v>2.986041611077107</v>
       </c>
       <c r="N7" t="n">
-        <v>16.89946490565958</v>
+        <v>16.83487535541107</v>
       </c>
       <c r="O7" t="n">
-        <v>4.110895876285312</v>
+        <v>4.103032458488608</v>
       </c>
       <c r="P7" t="n">
-        <v>376.4711954738768</v>
+        <v>376.4754525182024</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -26745,28 +26843,28 @@
         <v>0.1273</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1405937626141022</v>
+        <v>0.1389742072299004</v>
       </c>
       <c r="J8" t="n">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="K8" t="n">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0486138314204756</v>
+        <v>0.04787273083412968</v>
       </c>
       <c r="M8" t="n">
-        <v>3.950059521285552</v>
+        <v>3.9437132286674</v>
       </c>
       <c r="N8" t="n">
-        <v>24.7024330599458</v>
+        <v>24.62587191969202</v>
       </c>
       <c r="O8" t="n">
-        <v>4.970154228989861</v>
+        <v>4.962446162901117</v>
       </c>
       <c r="P8" t="n">
-        <v>378.9159162801054</v>
+        <v>378.9323215909438</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -26823,28 +26921,28 @@
         <v>0.0502</v>
       </c>
       <c r="I9" t="n">
-        <v>0.03357983206443488</v>
+        <v>0.02954854529647451</v>
       </c>
       <c r="J9" t="n">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="K9" t="n">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="L9" t="n">
-        <v>0.003660991251656087</v>
+        <v>0.002840437229156945</v>
       </c>
       <c r="M9" t="n">
-        <v>3.521408278222524</v>
+        <v>3.529747401281925</v>
       </c>
       <c r="N9" t="n">
-        <v>19.59639223901209</v>
+        <v>19.65024982947121</v>
       </c>
       <c r="O9" t="n">
-        <v>4.426781250413453</v>
+        <v>4.432860231213162</v>
       </c>
       <c r="P9" t="n">
-        <v>379.5522015126968</v>
+        <v>379.5930409373917</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -26901,28 +26999,28 @@
         <v>0.0552</v>
       </c>
       <c r="I10" t="n">
-        <v>0.05776105812605289</v>
+        <v>0.0561174586657122</v>
       </c>
       <c r="J10" t="n">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="K10" t="n">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="L10" t="n">
-        <v>0.01607672759311729</v>
+        <v>0.01528164726037917</v>
       </c>
       <c r="M10" t="n">
-        <v>2.963690112506149</v>
+        <v>2.961282286258516</v>
       </c>
       <c r="N10" t="n">
-        <v>13.0390064947457</v>
+        <v>13.00930980256179</v>
       </c>
       <c r="O10" t="n">
-        <v>3.610956451516094</v>
+        <v>3.606842081733242</v>
       </c>
       <c r="P10" t="n">
-        <v>384.5143797916364</v>
+        <v>384.5310282916824</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -26960,7 +27058,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K504"/>
+  <dimension ref="A1:K506"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55691,6 +55789,120 @@
         </is>
       </c>
     </row>
+    <row r="505">
+      <c r="A505" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-05 22:11:21+00:00</t>
+        </is>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>-34.98895427192115,173.4799305496598</t>
+        </is>
+      </c>
+      <c r="C505" t="inlineStr">
+        <is>
+          <t>-34.989512390432004,173.48049932774552</t>
+        </is>
+      </c>
+      <c r="D505" t="inlineStr">
+        <is>
+          <t>-34.98965083149676,173.4813534592432</t>
+        </is>
+      </c>
+      <c r="E505" t="inlineStr">
+        <is>
+          <t>-34.989778709707366,173.4822430504372</t>
+        </is>
+      </c>
+      <c r="F505" t="inlineStr">
+        <is>
+          <t>-34.990008903200874,173.48309820378606</t>
+        </is>
+      </c>
+      <c r="G505" t="inlineStr">
+        <is>
+          <t>-34.990151973120135,173.48396316579664</t>
+        </is>
+      </c>
+      <c r="H505" t="inlineStr">
+        <is>
+          <t>-34.99024082661416,173.48482550148503</t>
+        </is>
+      </c>
+      <c r="I505" t="inlineStr">
+        <is>
+          <t>-34.99027993169808,173.4857184512226</t>
+        </is>
+      </c>
+      <c r="J505" t="inlineStr">
+        <is>
+          <t>-34.99028613962653,173.48661993468724</t>
+        </is>
+      </c>
+      <c r="K505" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-28 22:17:40+00:00</t>
+        </is>
+      </c>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>-34.9889405697782,173.4799430471991</t>
+        </is>
+      </c>
+      <c r="C506" t="inlineStr">
+        <is>
+          <t>-34.989502717977295,173.480504166199</t>
+        </is>
+      </c>
+      <c r="D506" t="inlineStr">
+        <is>
+          <t>-34.98964106318149,173.4813555519101</t>
+        </is>
+      </c>
+      <c r="E506" t="inlineStr">
+        <is>
+          <t>-34.98977238359779,173.48224526142505</t>
+        </is>
+      </c>
+      <c r="F506" t="inlineStr">
+        <is>
+          <t>-34.99000101296121,173.483101317323</t>
+        </is>
+      </c>
+      <c r="G506" t="inlineStr">
+        <is>
+          <t>-34.990143494440275,173.4839652871817</t>
+        </is>
+      </c>
+      <c r="H506" t="inlineStr">
+        <is>
+          <t>-34.99023875578983,173.48482564012141</t>
+        </is>
+      </c>
+      <c r="I506" t="inlineStr">
+        <is>
+          <t>-34.99028200331007,173.48571833121795</t>
+        </is>
+      </c>
+      <c r="J506" t="inlineStr">
+        <is>
+          <t>-34.99028336217627,173.48662031839808</t>
+        </is>
+      </c>
+      <c r="K506" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
